--- a/K_2_Cents_Model_Spec.xlsx
+++ b/K_2_Cents_Model_Spec.xlsx
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built: 2026-06-24 13:55 UTC  |  Anchored to FIFA Fantasy WC2026 scoring schema</t>
+          <t>Built: 2026-06-24 16:31 UTC  |  Anchored to FIFA Fantasy WC2026 scoring schema</t>
         </is>
       </c>
     </row>
@@ -4193,13 +4193,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>90.5</v>
+        <v>89.2</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>95.5</v>
+        <v>92</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>88.8</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="18">
@@ -4215,7 +4215,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -4225,13 +4225,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>67.90000000000001</v>
+        <v>165.7</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>78.2</v>
+        <v>170.1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>56.1</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="20">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Lionel Messi (ARG)</t>
+          <t>Cody Gakpo (NED)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Lionel Messi (ARG)</t>
+          <t>Cody Gakpo (NED)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Lionel Messi (ARG)</t>
+          <t>Cody Gakpo (NED)</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Harry Kane (ENG) £10.5</t>
+          <t>Brian Brobbey (NED) £5.7</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Kylian Mbappé (FRA) £10.5</t>
+          <t>Kevin De Bruyne (BEL) £7.5</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Harry Kane (ENG) £10.5</t>
+          <t>Ryan Gravenberch (NED) £6.1</t>
         </is>
       </c>
     </row>
@@ -4315,17 +4315,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>[GK] ★Alireza Beiranvand (IRN) £4.2 0.2%</t>
+          <t>[GK] Thibaut Courtois (BEL) £4.9 12.3%</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>[GK] ★Eloy Room (CUW) £3.9 0.1%</t>
+          <t>[GK] Emiliano Martínez (ARG) £5.0 24.2%</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>[GK] ★Alireza Beiranvand (IRN) £4.2 0.2%</t>
+          <t>[GK] ★Yahia Fofana (CIV) £4.2 1.1%</t>
         </is>
       </c>
     </row>
@@ -4337,17 +4337,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Alexander Freeman (USA) £4.0 1.9%</t>
+          <t>[DEF] ★Noussair Mazraoui (MAR) £4.4 2.0%</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Facundo Medina (ARG) £4.0 1.8%</t>
+          <t>[DEF] Achraf Hakimi (MAR) £6.0 24.0%</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Djed Spence (ENG) £4.5 0.4%</t>
+          <t>[DEF] ★Noussair Mazraoui (MAR) £4.4 2.0%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Jorge Sánchez (MEX) £4.0 0.7%</t>
+          <t>[DEF] Cristian Romero (ARG) £4.9 6.8%</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Alexander Freeman (USA) £4.0 1.9%</t>
+          <t>[DEF] ★Guéla Doué (CIV) £3.9 1.6%</t>
         </is>
       </c>
     </row>
@@ -4381,17 +4381,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Jorge Sánchez (MEX) £4.0 0.7%</t>
+          <t>[DEF] ★Lisandro Martínez (ARG) £4.6 4.1%</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] Cristian Romero (ARG) £4.9 6.8%</t>
+          <t>[DEF] Joshua Kimmich (GER) £5.5 32.2%</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Ramin Rezaeian (IRN) £4.0 0.9%</t>
+          <t>[DEF] ★Facundo Medina (ARG) £4.0 1.8%</t>
         </is>
       </c>
     </row>
@@ -4403,17 +4403,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[MID] Michael Olise (FRA) £9.5 35.8%</t>
+          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8% VC</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Felix Nmecha (GER) £5.6 4.2%</t>
+          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8% VC</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>[MID] Ismael Saibari (MAR) £6.8 5.3%</t>
+          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8% VC</t>
         </is>
       </c>
     </row>
@@ -4425,17 +4425,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>[MID] Ismael Saibari (MAR) £6.8 5.3%</t>
+          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8%</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>[MID] Michael Olise (FRA) £9.5 35.8%</t>
+          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8%</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Keito Nakamura (JPN) £5.5 1.9%</t>
+          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.1%</t>
         </is>
       </c>
     </row>
@@ -4447,17 +4447,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Lionel Messi (ARG) £10.0 26.8% C</t>
+          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Lionel Messi (ARG) £10.0 26.8% C</t>
+          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Lionel Messi (ARG) £10.0 26.8% C</t>
+          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
         </is>
       </c>
     </row>
@@ -4469,17 +4469,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Erling Haaland (NOR) £10.5 30.3% VC</t>
+          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Erling Haaland (NOR) £10.5 30.3% VC</t>
+          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8% VC</t>
+          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8%</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Erling Haaland (NOR) £10.5 30.3%</t>
+          <t>[FWD] ★Brian Brobbey (NED) £5.7 0.7%</t>
         </is>
       </c>
     </row>
@@ -4513,17 +4513,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Felix Nmecha (GER) £5.6 4.2%</t>
+          <t>[MID] ★Ryan Gravenberch (NED) £6.1 1.9%</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>[MID] Ismael Saibari (MAR) £6.8 5.3%</t>
+          <t>[MID] ★Ryan Gravenberch (NED) £6.1 1.9%</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Maxi Araújo (URU) £6.4 0.7%</t>
+          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8%</t>
         </is>
       </c>
     </row>
@@ -4535,17 +4535,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Maxi Araújo (URU) £6.4 0.7%</t>
+          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.1%</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>[MID] Abbosbek Fayzullaev (UZB) £6.2 0.0%</t>
+          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.1%</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Bradley Barcola (FRA) £8.0 1.6%</t>
+          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.1%</t>
         </is>
       </c>
     </row>

--- a/K_2_Cents_Model_Spec.xlsx
+++ b/K_2_Cents_Model_Spec.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Factor catalog" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Data lineage" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Scoring schema" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Strategies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Models" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Chip strategy" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Anomalies &amp; edge cases" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built: 2026-06-24 16:31 UTC  |  Anchored to FIFA Fantasy WC2026 scoring schema</t>
+          <t>Built: 2026-06-24 18:52 UTC  |  Anchored to FIFA Fantasy WC2026 scoring schema</t>
         </is>
       </c>
     </row>
@@ -3929,26 +3929,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Three default strategies — K's SB-quotas + my aggression mapping</t>
+          <t>Three independent models — one squad each (Challenges)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SB-quota = target count of starting-15 picks from &lt;5% ownership band (±1 tolerance).</t>
+          <t>Each model scores the same player pool with a different philosophy. The 3 squads track separately like real fantasy teams.</t>
         </is>
       </c>
     </row>
@@ -3960,17 +3960,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>S1 — Balanced Hunter</t>
+          <t>M1 — Banker</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>S2 — Steady Banker</t>
+          <t>M2 — Form Hunter</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>S3 — Differential Maximizer</t>
+          <t>M3 — Stat Maximizer</t>
         </is>
       </c>
     </row>
@@ -3982,570 +3982,602 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Mid-aggression. Chases SB and contrarian fixture mismatches while keeping a spine of proven scorers.</t>
+          <t>Floor-heavy. Consistency, average points, SB track record. Premium picks on favored fixtures. Cleanest top-decile path on average rounds.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Low aggression. Floor-maximizing premium picks on favored fixtures. Cleanest top-10% path on average rounds.</t>
+          <t>Recency-weighted. Recent goals, started-pct, fotmob rating, last-round explosions. Punishes cold streaks even on strong fixtures.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Max aggression. Built for SB +2 hunting and rank-leap rounds. Higher variance, every SB-firing player a multiplier.</t>
+          <t>Pure FIFA-stats. Powerrank + position-routed per-90 + creativity + duels. Ignores ownership entirely — picks best player regardless of crowd.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SB-quota (target, ±1)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>9 of 15</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>5 of 15</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>12 of 15</t>
-        </is>
+          <t>Bracket weight w_B1 (PlayerOverall)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Floor weight (α)</t>
+          <t>Bracket weight w_B2 (WC Perf)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ceiling weight (β)</t>
+          <t>Bracket weight w_B3 (External)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>0.2</v>
-      </c>
       <c r="D8" s="5" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Differential weight (γ)</t>
+          <t>Bracket weight w_B4 (Fantasy meta)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Normalization mode</t>
+          <t>Post-boost sub-scores</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Ensemble mean (all 3)</t>
+          <t>(none — bracket-only)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Ensemble mean (all 3)</t>
+          <t>recent_form_streak (recent5/10 goals, POM, started_pct, last_round_pts)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Ensemble mean (all 3)</t>
+          <t>creativity_engine (chances_created, big_chances, touches_opp_box, ball-progressions) + powerrank_pure (atk/def/cre/gk)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Fixture-shape preference</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Any; anti_pick allowed on consensus_tight</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Lopsided; anti_pick not used</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Any; anti_pick allowed on consensus_tight</t>
-        </is>
+          <t>Fixture amplifier (B5 weight)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Budget mode</t>
+          <t>SB-quota (target, ±1)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Both (budget + unbudgeted)</t>
+          <t>9 of 15</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>6 of 15</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>3 of 15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Chip plan</t>
+          <t>Captain rule</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Wildcard → R16; 12th Man → R16; Max Captain → QF; Qual Boost → QF</t>
+          <t>argmax(ev_model × 2 + Σ ev_others over XI)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wildcard → group MD3 (if 5+ injuries) else hold; 12th Man → R16; Max Captain → QF</t>
+          <t>same</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Wildcard → QF (variance amplifier); 12th Man → R32; Max Captain → SF; Qual Boost → R16</t>
+          <t>same</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Budget mode</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Both (budget + unbudgeted)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>MD3 SNAPSHOT</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Formation</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>3-4-3</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>3-4-3</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>3-4-3</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Each model runs as its own Challenge — round-by-round actuals tracked against fantasy_player_round_stats. Transfer rules per FIFA Fantasy spec: 2 free MD2/MD3, unlimited R32, 4 R16/QF, 5 SF, 6 Final, -3 per extra.</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>same</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Budget spent (£m)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>80.8</v>
-      </c>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>CURRENT ROUND SNAPSHOT</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>SB-band picks (actual)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>13</v>
+          <t>Formation</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>3-4-3</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>3-4-3</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>3-5-2</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Projected pts (incl. captain)</t>
+          <t>Budget spent (£m)</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>165.7</v>
+        <v>89.2</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>170.1</v>
+        <v>90.5</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>141.6</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Captain</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Cody Gakpo (NED)</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Cody Gakpo (NED)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Cody Gakpo (NED)</t>
-        </is>
+          <t>SB-band picks (actual)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>Projected pts (incl. captain)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>103.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Captain</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Cody Gakpo (NED)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Cody Gakpo (NED)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Cody Gakpo (NED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>12th Man</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Brian Brobbey (NED) £5.7</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Kevin De Bruyne (BEL) £7.5</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Ryan Gravenberch (NED) £6.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>STARTING XI (MD3 snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Brian Brobbey (NED) £5.7</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Noussair Mazraoui (MAR) £4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>STARTING XI (current snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Balanced Hunter</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Steady Banker</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Differential Maximizer</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>[GK] Thibaut Courtois (BEL) £4.9 12.3%</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>[GK] Emiliano Martínez (ARG) £5.0 24.2%</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>[GK] ★Yahia Fofana (CIV) £4.2 1.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[DEF] ★Noussair Mazraoui (MAR) £4.4 2.0%</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>[DEF] Achraf Hakimi (MAR) £6.0 24.0%</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>[DEF] ★Noussair Mazraoui (MAR) £4.4 2.0%</t>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Form Hunter</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Stat Maximizer</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#1</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Facundo Medina (ARG) £4.0 1.8%</t>
+          <t>[GK] Thibaut Courtois (BEL) £4.9 12.3%</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>[DEF] Cristian Romero (ARG) £4.9 6.8%</t>
+          <t>[GK] Emiliano Martínez (ARG) £5.0 24.2%</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Guéla Doué (CIV) £3.9 1.6%</t>
+          <t>[GK] Emiliano Martínez (ARG) £5.0 24.2%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#2</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Lisandro Martínez (ARG) £4.6 4.1%</t>
+          <t>[DEF] ★Facundo Medina (ARG) £4.0 1.8%</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] Joshua Kimmich (GER) £5.5 32.2%</t>
+          <t>[DEF] ★Guéla Doué (CIV) £3.9 1.6%</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Facundo Medina (ARG) £4.0 1.8%</t>
+          <t>[DEF] Achraf Hakimi (MAR) £6.0 24.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8% VC</t>
+          <t>[DEF] ★Noussair Mazraoui (MAR) £4.4 2.0%</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8% VC</t>
+          <t>[DEF] Achraf Hakimi (MAR) £6.0 24.0%</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8% VC</t>
+          <t>[DEF] Cristian Romero (ARG) £4.9 6.8%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8%</t>
+          <t>[DEF] ★Lisandro Martínez (ARG) £4.6 4.1%</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8%</t>
+          <t>[DEF] Cristian Romero (ARG) £4.9 6.8%</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.1%</t>
+          <t>[DEF] Denzel Dumfries (NED) £5.7 14.8%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
+          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8% VC</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
+          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8% VC</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
+          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8% VC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
+          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8%</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
+          <t>[MID] Ismael Saibari (MAR) £6.8 5.3%</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8%</t>
+          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.1%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8%</t>
+          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8%</t>
+          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Brian Brobbey (NED) £5.7 0.7%</t>
+          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Ryan Gravenberch (NED) £6.1 1.9%</t>
+          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Ryan Gravenberch (NED) £6.1 1.9%</t>
+          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8%</t>
+          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8%</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8%</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Ryan Gravenberch (NED) £6.1 1.9%</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8%</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>[MID] Florian Wirtz (GER) £7.5 19.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>[MID] ★Leandro Trossard (BEL) £6.6 2.1%</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>[MID] ★Youri Tielemans (BEL) £6.1 1.1%</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.1%</t>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>[MID] Kevin De Bruyne (BEL) £7.5 5.6%</t>
         </is>
       </c>
     </row>

--- a/K_2_Cents_Model_Spec.xlsx
+++ b/K_2_Cents_Model_Spec.xlsx
@@ -15,6 +15,9 @@
     <sheet name="Chip strategy" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Anomalies &amp; edge cases" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Round Lock" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Archetypes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Decision Flow" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +60,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -104,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +129,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -505,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built: 2026-06-24 18:52 UTC  |  Anchored to FIFA Fantasy WC2026 scoring schema</t>
+          <t>Built: 2026-06-25 16:43 UTC  |  Anchored to FIFA Fantasy WC2026 scoring schema</t>
         </is>
       </c>
     </row>
@@ -689,6 +698,1042 @@
   <mergeCells count="1">
     <mergeCell ref="A14:D15"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player archetype clusters</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>K-means clustering in FIFA-stat + scoring-channel feature space. Two passes: retrospective (MD1+MD2 top-20% scorers) and prospective (full 1488 pool). Best-k chosen by silhouette across {6, 8, 10, 12}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ALGORITHM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Feature build</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Per-player aggregate from wc26_player_match_stats_wide (locked). p90 cols: AttemptAtGoal, AttemptAtGoalOnTarget, XG, Assists, Crosses, CrossesCompleted, PassesCompleted, Tackles, DefensivePressuresApplied, ForcedTurnovers, Corners, TotalDistance, GoalkeeperSaves. Plus wc_rating, FDH powerrank (attacking/defensive/creativity), price, %selected, scoring-channel composition (pts_from_goals/assists/cs/saves/sb/bonus pct).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Drop nulls</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Any feature column with &gt;40% null is dropped (avoids over-imputation in early-tournament samples). Remaining nulls filled with column median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Scale + cluster</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>StandardScaler + KMeans (n_init=10, random_state=42) at k ∈ {6,8,10,12}. Pick k with highest silhouette_score(Xs, labels).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Name each cluster</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>{TIER}_{POSITION}_{TOP_CHANNEL}_{TOP_STAT}_{OWN_BAND}. Tier from mean price (ELITE ≥9, MID_TIER ≥6, else BUDGET). Position = modal position. Top channel from scoring-channel composition (pts_from_goals / assists / cs / saves / sb / bonus). Top stat from highest mean p90 feature. Own band: DIFF if median %sel &lt; 5 else POPULAR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Exemplars</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Top-3 players per cluster by total fantasy points so far (or 0 if no R≤lock data yet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Attached to scoring frame</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>attach_archetypes(scored, retro, prospective) writes peer_archetype_retrospective + peer_archetype_prospective + similarity + top-3 examples onto every recommendation row. PWA reads these as reason chips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RETROSPECTIVE (MD1+MD2 TOP-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>k=6 · silhouette=0.217 · 6 clusters · 26 features</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Mean pts</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Top exemplars</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_MID_ASSISTS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Alexander Isak () 23pts · Felix Nmecha () 23pts · Ramin Rezaeian () 22pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_DEF_CS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Alexander Freeman () 23pts · Aymeric Laporte () 21pts · Sergiño Dest () 21pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>MID_TIER_FWD_GOALS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Lionel Messi () 33pts · Erling Haaland () 30pts · Deniz Undav () 28pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_MID_GOALS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Daichi Kamada () 22pts · Ismael Saibari () 21pts · Crysencio Summerville () 21pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>MID_TIER_MID_ASSISTS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Maxi Araújo () 23pts · Rubén Vargas () 18pts · Junya Ito () 12pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_GK_CS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Alireza Beiranvand () 14pts · Patrick Beach () 12pts · Vozinha () 12pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>PROSPECTIVE (FULL POOL, PRE-TOURNAMENT PROFILE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>k=8 · silhouette=0.543 · 8 clusters · 2 features</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Mean pts</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Top exemplars</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_MID_CS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>443</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Jesús Gallardo () 18pts · Yasin Ayari () 18pts · Kevin Pina () 14pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>ELITE_FWD_GOALS_TOTALDISTANCE_POPULAR</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Lionel Messi () 33pts · Erling Haaland () 30pts · Kylian Mbappé () 27pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_DEF_CS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>611</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Alexander Freeman () 23pts · Ramin Rezaeian () 22pts · Facundo Medina () 20pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>MID_TIER_MID_CS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Deniz Undav () 28pts · Jonathan David () 26pts · Alexander Isak () 23pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>MID_TIER_MID_GOALS_TOTALDISTANCE_POPULAR</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Vinícius Júnior () 20pts · Mikel Oyarzabal () 17pts · Ousmane Dembélé () 15pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_MID_CS_TOTALDISTANCE_DIFF</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Maxi Araújo () 23pts · Daichi Kamada () 22pts · Cyle Larin () 21pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_DEF_CS_TOTALDISTANCE_POPULAR</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Felix Nmecha () 23pts · Aymeric Laporte () 21pts · Sergiño Dest () 21pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>BUDGET_DEF_CS_TOTALDISTANCE_POPULAR</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Marc Cucurella () 17pts · Emiliano Martínez () 14pts · Joshua Kimmich () 10pts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision flow — inputs → factors → brackets → models → joint → outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>What gets read from where, what gets computed, how the 4 models combine into PWA outputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>INPUTS (under round lock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Parquet (in lock_dir)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Used for</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Per-round fantasy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>fantasy_player_round_stats.parquet (filtered)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Source of cumulative fantasy totals (rebuilt into stg_fantasy_player_totals). Drives B4 FantasyMeta — form, avg_pts, total_pts, consistency, last_round_points, scouting_bonus, sb_track multiplier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Per-match FIFA</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>wc26_player_match_stats_wide.parquet (filtered)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>53 spec'd FIFA stats per (player, match) — Goals, Assists, AttemptAtGoal(OnTarget), XG, Tackles, GoalkeeperSaves, CleanSheets, Passes(Completed), BallProgressions, SwitchesOfPlay, ChancesCreated, TouchesOppBox, DefensivePressures, etc. Rebuilt into stg_players_view.fifa_wc_* cols (SUM/AVG/MAX). Drives B2 WCPerfRating (per-90 + Bayesian shrinkage, position-routed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Per-match FDH powerrank</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>wc26_player_match_powerrank.parquet (filtered)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Attacking / defensive / creativity / defending_the_goal scores per (player, match). Rebuilt into stg_player_powerrank avg_*. Feeds B2 (30% weight) for position-conditional power-rank percentile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Identity + profile</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>fantasy_players.parquet, wc26_stg_players_view.parquet (career/value/recent-form cols preserved live)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Position, price, %selected, known_name, fifa_player_id↔fantasy_player_id mapping. Career rollups (club_senior_*, national_senior_*), market value (latest/peak), FotMob recent5/10/15 windows. Drives B1 PlayerOverall + B3 ExternalRatings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>FotMob WC tournament rollup</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>wc26_stg_players_view.fotmob_wc_* (live snapshot, partial leak)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>FotMob's tournament-stats endpoint — chances_created, big_chances, dribbles, duels_won, touches_opp_box, defensive_contributions, xg_against_on_pitch. Feeds B2 (FotMob branch). NOT round-filterable — see Round Lock sheet audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Fixtures + schedule</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>fantasy_round_matches.parquet, wc26_stg_matches.parquet (as-is)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Round 24-match window, home/away nation_id, kickoff_utc, stage, venue. Drives fixture cross-join in scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Markets</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>wc26_match_polymarket_markets.parquet, wc26_polymarket_match_volume.parquet (as-is)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Per-fixture Polymarket implied probabilities: moneyline (p_home_win/p_away_win/p_draw), over/under totals (0.5-9.5), BTTS, per-side scoring. Feeds goals_index + cs_index + p_btts in fixture profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Trends + weather</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>wc26_match_trends_365.parquet, wc26_match_weather.parquet (as-is)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Scores365 historic-trend rankings per fixture; weather cluster + temperature + humidity + roof_type + surface. Feeds B5 FixtureMultiplier modifiers (weather_drag, trend_top_confidence).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Nations identity</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>wc26_stg_nations.parquet, fantasy_squads.parquet (as-is)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Confederation, FIFA rank, pot, squad valuation. Drives nation_strength_composite in B1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Team match metrics</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>wc26_stg_team_match_metrics.parquet (filtered)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Per-team WC2026 match metrics. Used by team-strength derivations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Live %selected (NOT locked)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>refresh_live_percent_selected() — vercel /api/fifa-fantasy edge proxy</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Tick-fresh ownership for every fantasy_player_id. Overrides snapshot %selected before scoring. Drives differential / SB-eligibility math. Intentionally floats between re-runs of the same lock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ENSEMBLE FLOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>1. Archetype mining (shared)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>mine_archetypes_v2('retrospective') + mine_archetypes_v2('prospective')</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>data/eda/archetypes_*_v2.json — cluster definitions + player_clusters map. Both runs read the LOCKED parquets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2. Fixture profile (per round)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>assemble_fixture_profile(target_round)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>24 fixture rows: goals_index, cs_index_home/away, p_home_win/away_win/draw, p_btts, nation_strength_delta, fixture_shape ∈ {consensus_lopsided, consensus_tight, market_overconfident, composite_overconfident}, weather_cluster, trend_top_*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>3a. Score under each of 4 models</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>score_for_model(target, fx, model_id) → score_players_brackets() under that model's weights</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Per-player rows with b1_overall, b2_wc_perf, b3_external, b4_fantasy, b5_fixture_mult, bracket_sum, ev_bracket, ev_model (post-boosts applied for M2/M3/M4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>3b. Filters + anti-pick tag</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>apply_filters() then tag_anti_picks()</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Drops is_active=False + injured. Tags 2nd/3rd ranked players on the opponent side of consensus_tight fixtures as anti_picks (D-3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>3c. Reason chips</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>tag_chips()</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>HEDGE / DIFFERENTIAL / SB_TRACK_xN / SB_LIKELY / CEILING_HOT / FAVORED_FIXTURE / TREND_&lt;CAT&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>3d. Attach archetypes</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>attach_archetypes(scored, retro, prospective)</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>archetype_retrospective + sim + 3 examples; archetype_prospective + sim + 3 examples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>4. Joint output</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>build_joint_picks(model_outputs, top_n=30)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>consensus (in ≥2 models' top-30, sorted by max_ev), surprises (in exactly 1 model's top-30), per_position_top (15 FWD / 15 MID / 15 DEF / 5 GK by max ev_model across ALL models — pulls from FULL scored frame, not the top-30 union).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>5. Per-model squads</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>assemble_strategy_squad (M1/M2/M3) or assemble_sb_hunter_squad (M4)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>One challenge squad per model: 2/5/5/3 quota, ≤3/nation, £100m budget, captain + vice + 12th-man. Also emits an unbudgeted variant for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>6. Position suggestor (legacy)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>build_position_suggestor(banker)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>wc26_fantasy_position_suggestor.json — kept for back-compat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>7. Round tracking</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>build_round_tracking(squads_by_round)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Closed-round actuals joined against fantasy_player_round_stats; running totals per model. Auto-pulls prior round snapshots from data/processed/history/round_NN/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>8. PWA emit</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>_emit_pwa_json.py (downstream) + parquet→json mirroring inside 17</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Writes data/processed/json/*.json which the PWA fetches at /data/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>PWA RENDERING (consumer side)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Suggested Picks → By Position</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>joint.per_position_top — 15 FWD / 15 MID / 15 DEF / 5 GK. Position chip filters to one position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Suggested Picks → High Confidence</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>joint.consensus — players in ≥2 model top-30 lists. Tile shows model attribution chips (M1/M2/M3/M4 short labels, no EV numbers — feedback removed the per-model EV).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Suggested Picks → Per-Model Surprises</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>joint.surprises grouped by model_id. Tile design same as consensus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Suggested Picks → SB Eligible</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Deduped pool from joint.per_position_top + filter to live %sel &lt; 5%. Honours position chips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Fantasy Challenge</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>4 strategy_squads (one per model). Tap to drill in: FIFA-style round-picker tabs across the top, total pts huge, captain marked, per-tile live/finished badge.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -699,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -708,10 +1753,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -724,435 +1769,145 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EDA |corr| col shows MD1+MD2 max |corr| with actual fantasy points. 'Status' = ACTIVE / DROPPED / DEFERRED.</t>
+          <t>EDA |corr| col = MAX |corr| between the factor (computed over MD1+MD2) and actual MD1+MD2 fantasy points. CAVEAT: this is CONTEMPORANEOUS correlation — not predictive validation. Factors that ARE the events points are computed from (goals, assists, clean sheets, form, avg_points) will show inflated |corr| by construction. See AUTOCORRELATION AUDIT below — autocorrelated factors are flagged with handling notes in the Definition column. 'Status' = ACTIVE / DROPPED / DEFERRED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>AUTOCORRELATION AUDIT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Position scope</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Source table.column</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Transform</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>EDA |corr|</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Weight (default)</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Definition / notes</t>
+          <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Why does |corr| look so high for some factors?</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Stage flip multiplier</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Fixture</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>wc26_stg_matches.stage</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>group=1.00, R32=1.15, R16=1.25, QF=1.40, SF+=1.55</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Higher stakes → weaker teams overperform; multiplies fixture indices.</t>
+          <t>Fantasy points are LITERALLY a function of in-match events: goal=4-6pts, assist=3pts, clean_sheet=4/5pts, save_chunks=+1, etc. Any factor that IS one of those event counts (B7 shots_on_target=0.65, B11 CS_prior=0.44, C1 XG=0.63, C2 assists=0.42) trivially correlates with points because it's almost computed from the same data. Same trap for LAGGED-TARGET factors (form, avg_pts, total_pts) — they ARE past fantasy points being used to predict future fantasy points.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>A2a</t>
+          <t>How is this handled in the model?</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Moneyline volume (consensus strength)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Fixture</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>wc26_polymarket_match_volume.volume_moneyline</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Percentile rank → 0..1 confidence weight on A2b</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Gates A2b's confidence — low volume = soft signal.</t>
+          <t>Three mechanisms: (1) ROUND-LOCK isolates 'lagged' from 'concurrent' — R3 emits only see ≤R2 stats, so B4 Fantasy Meta becomes a genuinely lagged signal, not a sneak preview of R3 itself. (2) DAMPENERS — C-NEW avg_points carries a hard ×0.3 coefficient; form prefers independent fotmob_rating (0.46) over fantasy.form (0.80). (3) ENSEMBLE DIVERSIFICATION — M3 Stat Maximizer holds w_B4 at 0.10 (vs 0.35-0.40 in M1/M4) so the consensus signal isn't dominated by lagged points.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>A2b</t>
+          <t>Which factors are autocorrelated with the target?</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Moneyline lopsidedness</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Fixture</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>wc26_match_polymarket_markets (moneyline)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>p_home_win − p_away_win</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>HEAVY</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Signed [-1, +1]; positive = home favored. Drives consensus_lopsided shape.</t>
+          <t>HIGH risk (lagged target itself): C5 form 0.80 / C-NEW avg_points 0.83 / Bracket B4 (uses form, avg_pts, total_pts, last_round_points). MEDIUM (event-coupled — same window): B7 SoT 0.65 / B11 CS_prior 0.44 / C1 XG 0.63 / B14 powerrank 0.63. LOW (independent / pre-tournament priors): A14 nation_strength 0.71 / A2b moneyline_lopsidedness / A4 goals_index / B1 start_prob 0.17 / A12 365_trends. Independent signals are the model's predictive backbone; event-coupled features are gated by the round-lock so they're lagged not concurrent.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>A2c</t>
+          <t>Is M3 Stat Maximizer the 'autocorrelation-free' counter-weight?</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Other-market depth</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Fixture</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>drop</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Corr 0.09 with goal totals on MD1+MD2 — no signal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Per-side clean-sheet probability</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Fixture</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>DEF, GK, MID</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>wc26_match_polymarket_markets (team-total-{home|away}-0pt5)</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>p_side_cs = 1 - p(opp scores 0.5+)</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>HEAVY</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Per-side derivation from O/U 0.5 Yes-price markets.</t>
+          <t>Yes — by design. M3 weights B2 WC Perf at 0.50 (per-match FIFA stats — event-coupled but lagged via lock) and B4 Fantasy Meta at just 0.10. Its disagreement with M1 Banker (w_B4=0.35) is what makes consensus picks meaningful — when M3 AND M1 agree, the player is good both by independent stats and by lagged fantasy meta. Surprises from M3 alone tend to be undervalued by the fantasy market because they're not yet showing up in pts/form.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Over/under 2.5 goals (goals_index)</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Fixture</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>wc26_match_polymarket_markets (total-2pt5)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>p(over 2.5) × weather mod × roof mod</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>HEAVY</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Drives goal_prob ceiling component.</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>FACTOR INVENTORY</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Per-player goalscorer odds</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Fixture/Player</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>FWD, MID</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>wc26_match_polymarket_markets (anytime_goalscorer)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Direct implied prob; null fallback to fifa_wc_XG</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE (sparse)</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Polymarket coverage thin — only 16/104 matches; fallback dominates.</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Position scope</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Source table.column</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Transform</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>EDA |corr|</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Weight (default)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Definition / notes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Referee discipline</t>
+          <t>Stage flip multiplier</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1167,12 +1922,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_referee_profile.yellow_pg</t>
+          <t>wc26_stg_matches.stage</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Normalize vs panel median → card_index 0..1</t>
+          <t>group=1.00, R32=1.15, R16=1.25, QF=1.40, SF+=1.55</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1182,7 +1937,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1192,19 +1947,19 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Multiplied with C-family attackers in high-card fixtures.</t>
+          <t>Higher stakes → weaker teams overperform; multiplies fixture indices.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A2a</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Weather cluster</t>
+          <t>Moneyline volume (consensus strength)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1219,22 +1974,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>wc26_match_weather + wc26_stg_stadiums.surface/roof_type</t>
+          <t>wc26_polymarket_match_volume.volume_moneyline</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>4 EDA clusters: 0 mild, 1 hot/dry, 2 altitude, 3 wet. Modifiers in D-6.</t>
+          <t>Percentile rank → 0..1 confidence weight on A2b</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>0.27 (cluster 1 draw rate)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>light</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1244,19 +1999,19 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Cluster 1: goals×0.92, cs×1.10. Cluster 2: goals×0.88. Retractable roof: goals×1.15.</t>
+          <t>Gates A2b's confidence — low volume = soft signal.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A2b</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Stadium altitude</t>
+          <t>Moneyline lopsidedness</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1271,44 +2026,44 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>wc26_match_polymarket_markets (moneyline)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>p_home_win − p_away_win</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>HEAVY</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>DROPPED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Subsumed into weather cluster 2 (altitude venues).</t>
+          <t>Signed [-1, +1]; positive = home favored. Drives consensus_lopsided shape.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A2c</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>FIFA-rank gap</t>
+          <t>Other-market depth</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1323,44 +2078,44 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_nations.fifa_rank</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>home_rank − away_rank, bucketed</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>0.71 (nation_strength as proxy)</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>DROPPED</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Underlies §I.1 static profile + A14.</t>
+          <t>Corr 0.09 with goal totals on MD1+MD2 — no signal.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Nation tournament form</t>
+          <t>Per-side clean-sheet probability</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1370,17 +2125,17 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DEF, GK, MID</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Derived from fantasy_round_matches prior rounds</t>
+          <t>wc26_match_polymarket_markets (team-total-{home|away}-0pt5)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>W=3 D=1 L=0 over up-to-2 matches</t>
+          <t>p_side_cs = 1 - p(opp scores 0.5+)</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1390,7 +2145,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>HEAVY</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1400,19 +2155,19 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Folded into §I.2 nation_total_strength.</t>
+          <t>Per-side derivation from O/U 0.5 Yes-price markets.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>WC champion implied prob</t>
+          <t>Over/under 2.5 goals (goals_index)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1427,12 +2182,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>wc26_polymarket_winner_history (latest snapshot)</t>
+          <t>wc26_match_polymarket_markets (total-2pt5)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Direct 0..1</t>
+          <t>p(over 2.5) × weather mod × roof mod</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1442,7 +2197,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>HEAVY</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1452,71 +2207,71 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Long-term sentiment signal beyond this fixture.</t>
+          <t>Drives goal_prob ceiling component.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>365scores top trend</t>
+          <t>Per-player goalscorer odds</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Fixture</t>
+          <t>Fixture/Player</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>FWD, MID</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_match_trends_365</t>
+          <t>wc26_match_polymarket_markets (anytime_goalscorer)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Category × pct-bucket calibration multiplier (EDA §4)</t>
+          <t>Direct implied prob; null fallback to fifa_wc_XG</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>0.62 baseline</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>HEAVY (when category matches)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (sparse)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>doubleChance≥0.9: 95% hit (n=21). BTTS≥0.9: 100% (n=4). Result-type: 44-75% discount.</t>
+          <t>Polymarket coverage thin — only 16/104 matches; fallback dominates.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>365scores decider trend</t>
+          <t>Referee discipline</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1531,12 +2286,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_match_trends_365 (confidenceTrendIds)</t>
+          <t>wc26_stg_referee_profile.yellow_pg</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Same calibration as A12</t>
+          <t>Normalize vs panel median → card_index 0..1</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1546,7 +2301,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>light</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1556,19 +2311,19 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Confirmation strength back-up signal.</t>
+          <t>Multiplied with C-family attackers in high-card fixtures.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Nation strength delta</t>
+          <t>Weather cluster</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1583,22 +2338,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>§I composite (I.1 + I.2 + I.4)</t>
+          <t>wc26_match_weather + wc26_stg_stadiums.surface/roof_type</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Stage-conditional weights; D-2</t>
+          <t>4 EDA clusters: 0 mild, 1 hot/dry, 2 altitude, 3 wet. Modifiers in D-6.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.27 (cluster 1 draw rate)</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>HEAVY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1608,19 +2363,19 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Independent of Polymarket; signed [-1, +1] home perspective.</t>
+          <t>Cluster 1: goals×0.92, cs×1.10. Cluster 2: goals×0.88. Retractable roof: goals×1.15.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Market-vs-composite divergence</t>
+          <t>Stadium altitude</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1635,12 +2390,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>|A2b - A14|</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Abs value → upset opportunity flag</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1650,34 +2405,34 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>DROPPED</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>High divergence → market_overconfident or composite_overconfident shape.</t>
+          <t>Subsumed into weather cluster 2 (altitude venues).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Start probability</t>
+          <t>FIFA-rank gap</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Fixture</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1687,22 +2442,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>recent5_started_pct → recent10_started_pct → 0.5</t>
+          <t>wc26_stg_nations.fifa_rank</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Direct 0..1, fallback cascade</t>
+          <t>home_rank − away_rank, bucketed</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.71 (nation_strength as proxy)</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>HEAVY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -1712,44 +2467,44 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Gates appearance points + every other position contribution.</t>
+          <t>Underlies §I.1 static profile + A14.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>GK saves rate × opp goals_index</t>
+          <t>Nation tournament form</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Fixture</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>fifa_wc_GoalkeeperSaves / appearances</t>
+          <t>Derived from fantasy_round_matches prior rounds</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Per-mode denom × 1/3 (every 3 saves = +1)</t>
+          <t>W=3 D=1 L=0 over up-to-2 matches</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1764,44 +2519,44 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Maps to FIFA's every-3-saves +1 schema.</t>
+          <t>Folded into §I.2 nation_total_strength.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>DEF tackles per 90</t>
+          <t>WC champion implied prob</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Fixture</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>fantasy_totals.tackles</t>
+          <t>wc26_polymarket_winner_history (latest snapshot)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Per-mode denom (no points-bonus for DEF tackles)</t>
+          <t>Direct 0..1</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1816,49 +2571,49 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Activity proxy; helps CS prediction indirectly.</t>
+          <t>Long-term sentiment signal beyond this fixture.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>MID tackle volume</t>
+          <t>365scores top trend</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Fixture</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>fantasy_totals.tackles</t>
+          <t>wc26_stg_match_trends_365</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Per-mode denom × 1/3 (FIFA: every 3 tackles → +1)</t>
+          <t>Category × pct-bucket calibration multiplier (EDA §4)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.62 baseline</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>HEAVY (when category matches)</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -1868,44 +2623,44 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Reframed from binary floor (was 4.5/app) to ceiling-contributor.</t>
+          <t>doubleChance≥0.9: 95% hit (n=21). BTTS≥0.9: 100% (n=4). Result-type: 44-75% discount.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>B6</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>MID chances-created volume</t>
+          <t>365scores decider trend</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Fixture</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>fantasy_totals.chances_created</t>
+          <t>wc26_stg_match_trends_365 (confidenceTrendIds)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Per-mode denom × 1/2 (every 2 CC → +1)</t>
+          <t>Same calibration as A12</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1920,44 +2675,44 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Same reframe — volume contributor, not floor gate.</t>
+          <t>Confirmation strength back-up signal.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>B7</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>FWD shots-on-target volume</t>
+          <t>Nation strength delta</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Fixture</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>fifa_wc_AttemptAtGoalOnTarget OR fantasy_totals.shots_on_target</t>
+          <t>§I composite (I.1 + I.2 + I.4)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Per-mode denom × 1/2 (every 2 SoT → +1)</t>
+          <t>Stage-conditional weights; D-2</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1972,49 +2727,49 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Strong predictor of FWD output.</t>
+          <t>Independent of Polymarket; signed [-1, +1] home perspective.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>DEF clean-sheet prior</t>
+          <t>Market-vs-composite divergence</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Fixture</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>fifa_wc_CleanSheets / appearances</t>
+          <t>|A2b - A14|</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>× A3 (fixture per-side CS prob) × 5 pts</t>
+          <t>Abs value → upset opportunity flag</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>HEAVY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2024,19 +2779,19 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Maps to FIFA's DEF CS bonus (+5).</t>
+          <t>High divergence → market_overconfident or composite_overconfident shape.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Power-rank within team</t>
+          <t>Start probability</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2051,17 +2806,17 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_player_powerrank.avg_*_score</t>
+          <t>recent5_started_pct → recent10_started_pct → 0.5</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Position-conditional: atk→FWD, def→DEF, cre→MID, gk→GK</t>
+          <t>Direct 0..1, fallback cascade</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2076,49 +2831,49 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Strong cross-position signal.</t>
+          <t>Gates appearance points + every other position contribution.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Goal probability</t>
+          <t>GK saves rate × opp goals_index</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Ceiling</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>FWD, MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>fifa_wc_XG / denom + recent5/10/15_goals decay</t>
+          <t>fifa_wc_GoalkeeperSaves / appearances</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Decay weights {0.5, 0.3, 0.2} × goals_index × 2</t>
+          <t>Per-mode denom × 1/3 (every 3 saves = +1)</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>0.63 (fifa_wc_XG)</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>HEAVY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2128,49 +2883,49 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Combined per-mode XG and recent goal rate.</t>
+          <t>Maps to FIFA's every-3-saves +1 schema.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Assist probability</t>
+          <t>DEF tackles per 90</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Ceiling</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MID, FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>fifa_wc_Assists / denom + fotmob_wc_big_chances_created</t>
+          <t>fantasy_totals.tackles</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Combined index × goals_index × 3 pts</t>
+          <t>Per-mode denom (no points-bonus for DEF tackles)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>HEAVY</t>
+          <t>light</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -2180,44 +2935,44 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Maps to +3 assist points.</t>
+          <t>Activity proxy; helps CS prediction indirectly.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Form multiplier</t>
+          <t>MID tackle volume</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Ceiling</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>recent5_fotmob_rating (independent) OR fantasy.form</t>
+          <t>fantasy_totals.tackles</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>((rating - 6.0) / 4.0).clip(-0.15, 0.20) + 1.0 → multiplier 0.85-1.20</t>
+          <t>Per-mode denom × 1/3 (FIFA: every 3 tackles → +1)</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>0.46 (fotmob, independent); 0.80 (form, autocorr)</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2232,39 +2987,39 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Prefer fotmob rating — form is partly autocorrelated with points.</t>
+          <t>Reframed from binary floor (was 4.5/app) to ceiling-contributor.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>B6</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>FotMob WC creativity</t>
+          <t>MID chances-created volume</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Ceiling</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>MID, FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>fotmob_wc_big_chances_created + fotmob_wc_touches_opp_box</t>
+          <t>fantasy_totals.chances_created</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Combined index 0..1</t>
+          <t>Per-mode denom × 1/2 (every 2 CC → +1)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2284,49 +3039,49 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Sub-component of C1/C2.</t>
+          <t>Same reframe — volume contributor, not floor gate.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>C-NEW</t>
+          <t>B7</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>avg_points lag-1 prior</t>
+          <t>FWD shots-on-target volume</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Ceiling/Floor</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>fantasy_players.avg_points</t>
+          <t>fifa_wc_AttemptAtGoalOnTarget OR fantasy_totals.shots_on_target</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>× 0.3 dampener (autocorrelation)</t>
+          <t>Per-mode denom × 1/2 (every 2 SoT → +1)</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>HEAVY</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2336,49 +3091,49 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Added from EDA §10 broad sweep; weighted low to avoid lock-in.</t>
+          <t>Strong predictor of FWD output.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>C-NEW</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>recent5_player_of_the_match</t>
+          <t>DEF clean-sheet prior</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Ceiling</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_players_view.recent5_player_of_the_match</t>
+          <t>fifa_wc_CleanSheets / appearances</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>× 0.5 small bonus</t>
+          <t>× A3 (fixture per-side CS prob) × 5 pts</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>HEAVY</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2388,24 +3143,24 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Added from EDA §10.</t>
+          <t>Maps to FIFA's DEF CS bonus (+5).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Live %selected (SB sigmoid)</t>
+          <t>Power-rank within team</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Differential</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2415,17 +3170,17 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>fantasy_players.percent_selected</t>
+          <t>wc26_stg_player_powerrank.avg_*_score</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>1 / (1 + exp((pct − 5) / 1)) — sigmoid gate around 5%</t>
+          <t>Position-conditional: atk→FWD, def→DEF, cre→MID, gk→GK</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>0.47 (POSITIVE)</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -2435,49 +3190,49 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE (reframed)</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Raw ownership correlates POSITIVELY with points (popular = quality). Differential value lives ONLY on the +2 SB event.</t>
+          <t>Strong cross-position signal.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>SB track record</t>
+          <t>Goal probability</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Differential</t>
+          <t>Ceiling</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>FWD, MID</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_fantasy_player_totals.scouting_bonus</t>
+          <t>fifa_wc_XG / denom + recent5/10/15_goals decay</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>× (1 + 0.2 × min(sb_total, 5)) multiplier on D1</t>
+          <t>Decay weights {0.5, 0.3, 0.2} × goals_index × 2</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.63 (fifa_wc_XG)</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2492,76 +3247,76 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Already-earned SBs flag who clears the 4-pt threshold.</t>
+          <t>Combined per-mode XG and recent goal rate.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Ownership trend</t>
+          <t>Assist probability</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Differential</t>
+          <t>Ceiling</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>MID, FWD</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>fantasy_players.rounds_selected_json (Δ last 2 rounds)</t>
+          <t>fifa_wc_Assists / denom + fotmob_wc_big_chances_created</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Rising fast → cap D1; falling → boost</t>
+          <t>Combined index × goals_index × 3 pts</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>HEAVY</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Implementation: pending — needs to parse rounds_selected_json.</t>
+          <t>Maps to +3 assist points.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Editorial one-to-watch</t>
+          <t>Form multiplier</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Differential</t>
+          <t>Ceiling</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2571,74 +3326,74 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>fantasy_players.one_to_watch</t>
+          <t>recent5_fotmob_rating (independent) OR fantasy.form</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>+0.3 small lift</t>
+          <t>((rating - 6.0) / 4.0).clip(-0.15, 0.20) + 1.0 → multiplier 0.85-1.20</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.46 (fotmob, independent); 0.80 (form, autocorr)</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Column not exposed in current snapshot — defaulting to False.</t>
+          <t>Prefer fotmob rating — form is partly autocorrelated with points.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>I.1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Static profile</t>
+          <t>FotMob WC creativity</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>§I (nation)</t>
+          <t>Ceiling</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>All (fixture-level)</t>
+          <t>MID, FWD</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>trophies_won + fifa_rank + squad_valuation + is_host + group + confederation</t>
+          <t>fotmob_wc_big_chances_created + fotmob_wc_touches_opp_box</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>norm01 components, weighted</t>
+          <t>Combined index 0..1</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>0.33 (group stage)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -2648,24 +3403,24 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Tapers across stages per D-2: group 0.33 → KO 0.10.</t>
+          <t>Sub-component of C1/C2.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>C-NEW</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Tournament metrics (per-match)</t>
+          <t>avg_points lag-1 prior</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>§I (nation)</t>
+          <t>Ceiling/Floor</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2675,22 +3430,22 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_team_match_metrics (24+ metrics aggregated)</t>
+          <t>fantasy_players.avg_points</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>All divided by matches_played (no raw totals)</t>
+          <t>× 0.3 dampener (autocorrelation)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>0.33 (group)</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -2700,24 +3455,24 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Per-match normalization avoids fixture-count skew.</t>
+          <t>Added from EDA §10 broad sweep; weighted low to avoid lock-in.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>C-NEW</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Heavy hitter / clutch</t>
+          <t>recent5_player_of_the_match</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>§I (nation)</t>
+          <t>Ceiling</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2727,49 +3482,49 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>upset_win_rate, knockout_overperformance, clutch_close_score_rate</t>
+          <t>wc26_stg_players_view.recent5_player_of_the_match</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Multiplier centered at 1.0 (D-4)</t>
+          <t>× 0.5 small bonus</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>1.0 (no-op)</t>
+          <t>light</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Backfill from hand-curated CSV in later phase.</t>
+          <t>Added from EDA §10.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Player cumulative strength</t>
+          <t>Live %selected (SB sigmoid)</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>§I (nation)</t>
+          <t>Differential</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2779,82 +3534,446 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>wc26_stg_player_powerrank summed per nation</t>
+          <t>fantasy_players.percent_selected</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Sanity check on I.2; weighted sum 0.3 atk + 0.3 def + 0.2 cre + 0.2 gk</t>
+          <t>1 / (1 + exp((pct − 5) / 1)) — sigmoid gate around 5%</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.47 (POSITIVE)</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>0.34 (group) → 0.50 (KO)</t>
+          <t>HEAVY</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (reframed)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Cross-check: if I.2/I.4 disagree → 'individual talent but poor cohesion'.</t>
+          <t>Raw ownership correlates POSITIVELY with points (popular = quality). Differential value lives ONLY on the +2 SB event.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>SB track record</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Differential</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>wc26_stg_fantasy_player_totals.scouting_bonus</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>× (1 + 0.2 × min(sb_total, 5)) multiplier on D1</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>HEAVY</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Already-earned SBs flag who clears the 4-pt threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Ownership trend</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Differential</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>fantasy_players.rounds_selected_json (Δ last 2 rounds)</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Rising fast → cap D1; falling → boost</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Implementation: pending — needs to parse rounds_selected_json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Editorial one-to-watch</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Differential</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>fantasy_players.one_to_watch</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>+0.3 small lift</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Column not exposed in current snapshot — defaulting to False.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>I.1</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Static profile</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>§I (nation)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>All (fixture-level)</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>trophies_won + fifa_rank + squad_valuation + is_host + group + confederation</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>norm01 components, weighted</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>0.33 (group stage)</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Tapers across stages per D-2: group 0.33 → KO 0.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>I.2</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Tournament metrics (per-match)</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>§I (nation)</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>wc26_stg_team_match_metrics (24+ metrics aggregated)</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>All divided by matches_played (no raw totals)</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>0.33 (group)</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Per-match normalization avoids fixture-count skew.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>I.3</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Heavy hitter / clutch</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>§I (nation)</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>upset_win_rate, knockout_overperformance, clutch_close_score_rate</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Multiplier centered at 1.0 (D-4)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>1.0 (no-op)</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Backfill from hand-curated CSV in later phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>I.4</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Player cumulative strength</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>§I (nation)</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>wc26_stg_player_powerrank summed per nation</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Sanity check on I.2; weighted sum 0.3 atk + 0.3 def + 0.2 cre + 0.2 gk</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>0.34 (group) → 0.50 (KO)</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Cross-check: if I.2/I.4 disagree → 'individual talent but poor cohesion'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>I.5</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Nation-vs-Nation delta</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>§I (fixture)</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>home_total_strength − away_total_strength</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Normalized [-1, +1]; produces shape enum</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>0.71</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>HEAVY</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>The §I output that feeds A14.</t>
         </is>
@@ -3929,13 +5048,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3973,6 +5093,11 @@
           <t>M3 — Stat Maximizer</t>
         </is>
       </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>M4 — SB Hunter</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -3995,6 +5120,11 @@
           <t>Pure FIFA-stats. Powerrank + position-routed per-90 + creativity + duels. Ignores ownership entirely — picks best player regardless of crowd.</t>
         </is>
       </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Differential / SB-eligibility chaser. Custom assembler — anchors 3 fixed roles (2 'sure_shot_fwd' + 1 'influential_mid') then maximises sub-5% ownership across the remaining 12. High variance, high upside.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -4011,6 +5141,9 @@
       <c r="D6" s="5" t="n">
         <v>0.15</v>
       </c>
+      <c r="E6" s="5" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -4027,6 +5160,9 @@
       <c r="D7" s="5" t="n">
         <v>0.5</v>
       </c>
+      <c r="E7" s="5" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -4043,6 +5179,9 @@
       <c r="D8" s="5" t="n">
         <v>0.25</v>
       </c>
+      <c r="E8" s="5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -4059,6 +5198,9 @@
       <c r="D9" s="5" t="n">
         <v>0.1</v>
       </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4081,6 +5223,11 @@
           <t>creativity_engine (chances_created, big_chances, touches_opp_box, ball-progressions) + powerrank_pure (atk/def/cre/gk)</t>
         </is>
       </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>sb_track_bonus (sb_total ≥1 multiplier, sigmoid gate at 5% ownership, differential_kicker for &lt;2%)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -4097,6 +5244,9 @@
       <c r="D11" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -4119,465 +5269,597 @@
           <t>3 of 15</t>
         </is>
       </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>12 of 15</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Captain rule</t>
+          <t>Assembler</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>argmax(ev_model × 2 + Σ ev_others over XI)</t>
+          <t>generic (ev_model sort + SB-quota cap + ≤3/nation + £100m)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>assemble_sb_hunter_squad — anchors 2× sure_shot_fwd + 1× influential_mid by ev_model, fills rest from sub-5% pool</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Budget mode</t>
+          <t>Captain rule</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Both (budget + unbudgeted)</t>
+          <t>argmax(ev_model × 2 + Σ ev_others over XI)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>same</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>same</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>Budget mode</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Both (budget + unbudgeted)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>Tracking</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Each model runs as its own Challenge — round-by-round actuals tracked against fantasy_player_round_stats. Transfer rules per FIFA Fantasy spec: 2 free MD2/MD3, unlimited R32, 4 R16/QF, 5 SF, 6 Final, -3 per extra.</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>CURRENT ROUND SNAPSHOT</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Formation</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>3-4-3</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>3-4-3</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>3-5-2</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Budget spent (£m)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>99.59999999999999</v>
+          <t>Formation</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>3-4-3</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>3-4-3</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>3-5-2</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>3-5-2</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>SB-band picks (actual)</t>
+          <t>Budget spent (£m)</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>4</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>92.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Projected pts (incl. captain)</t>
+          <t>SB-band picks (actual)</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>105.1</v>
+        <v>6</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>103.8</v>
+        <v>4</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Captain</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Cody Gakpo (NED)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Cody Gakpo (NED)</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Cody Gakpo (NED)</t>
-        </is>
+          <t>Projected pts (incl. captain)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>103.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>Captain</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Cody Gakpo (NED)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Cody Gakpo (NED)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Cody Gakpo (NED)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Lionel Messi (ARG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>12th Man</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Brian Brobbey (NED) £5.7</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Brian Brobbey (NED) £5.7</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Noussair Mazraoui (MAR) £4.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Azzedine Ounahi (MAR) £6.2</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Cody Gakpo (NED) £7.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>STARTING XI (current snapshot)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Banker</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Form Hunter</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Stat Maximizer</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[GK] Thibaut Courtois (BEL) £4.9 12.3%</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>[GK] Emiliano Martínez (ARG) £5.0 24.2%</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>[GK] Emiliano Martínez (ARG) £5.0 24.2%</t>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>SB Hunter</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>#2</t>
+          <t>#1</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Facundo Medina (ARG) £4.0 1.8%</t>
+          <t>[GK] ★Alireza Beiranvand (IRN) £4.2 0.4%</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Guéla Doué (CIV) £3.9 1.6%</t>
+          <t>[GK] ★Vozinha (CPV) £3.9 2.3%</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>[DEF] Achraf Hakimi (MAR) £6.0 24.0%</t>
+          <t>[GK] Yahia Fofana (CIV) £4.2 5.1%</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>[GK] ★Bart Verbruggen (NED) £4.7 4.9%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#2</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Noussair Mazraoui (MAR) £4.4 2.0%</t>
+          <t>[DEF] Facundo Medina (ARG) £4.0 5.3%</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>[DEF] Achraf Hakimi (MAR) £6.0 24.0%</t>
+          <t>[DEF] ★Guéla Doué (CIV) £3.9 4.2%</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>[DEF] Cristian Romero (ARG) £4.9 6.8%</t>
+          <t>[DEF] ★Wilfried Singo (CIV) £4.4 2.5%</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>[DEF] ★Wilfried Singo (CIV) £4.4 2.5%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>[DEF] ★Lisandro Martínez (ARG) £4.6 4.1%</t>
+          <t>[DEF] Noussair Mazraoui (MAR) £4.4 5.0%</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>[DEF] Cristian Romero (ARG) £4.9 6.8%</t>
+          <t>[DEF] Virgil van Dijk (NED) £5.5 23.0%</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>[DEF] Denzel Dumfries (NED) £5.7 14.8%</t>
+          <t>[DEF] Noussair Mazraoui (MAR) £4.4 5.0%</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>[DEF] ★Nahuel Molina (ARG) £4.4 2.8%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8% VC</t>
+          <t>[DEF] ★Wilfried Singo (CIV) £4.4 2.5%</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8% VC</t>
+          <t>[DEF] Lisandro Martínez (ARG) £4.6 5.5%</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8% VC</t>
+          <t>[DEF] Achraf Hakimi (MAR) £6.0 29.4%</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>[DEF] ★Guéla Doué (CIV) £3.9 4.2%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Crysencio Summerville (NED) £5.3 3.8%</t>
+          <t>[MID] Brahim Díaz (MAR) £6.4 8.1%</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>[MID] Ismael Saibari (MAR) £6.8 5.3%</t>
+          <t>[MID] Ismael Saibari (MAR) £6.8 17.3%</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.1%</t>
+          <t>[MID] Brahim Díaz (MAR) £6.4 8.1% VC</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Ryan Gravenberch (NED) £6.1 2.4%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
+          <t>[MID] Crysencio Summerville (NED) £5.3 13.6%</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
+          <t>[MID] Crysencio Summerville (NED) £5.3 13.6%</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Cody Gakpo (NED) £7.7 4.7% C</t>
+          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.6%</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.6%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
+          <t>[FWD] Cody Gakpo (NED) £7.7 12.5% C</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
+          <t>[FWD] Cody Gakpo (NED) £7.7 12.5% C</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>[FWD] Lionel Messi (ARG) £10.0 26.8%</t>
+          <t>[FWD] Cody Gakpo (NED) £7.7 12.5% C</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>[FWD] Lionel Messi (ARG) £10.0 32.9% C</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8%</t>
+          <t>[FWD] Lionel Messi (ARG) £10.0 32.9% VC</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>[FWD] ★Deniz Undav (GER) £6.6 1.8%</t>
+          <t>[FWD] Lionel Messi (ARG) £10.0 32.9% VC</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.1%</t>
+          <t>[FWD] Lionel Messi (ARG) £10.0 32.9%</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>[FWD] ★Deniz Undav (GER) £6.6 3.4% VC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Ryan Gravenberch (NED) £6.1 1.9%</t>
+          <t>[FWD] ★Deniz Undav (GER) £6.6 3.4%</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>[MID] ★Brahim Díaz (MAR) £6.4 3.8%</t>
+          <t>[FWD] ★Deniz Undav (GER) £6.6 3.4%</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>[MID] Florian Wirtz (GER) £7.5 19.3%</t>
+          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.0%</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.0%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Ryan Gravenberch (NED) £6.1 2.4%</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.0%</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Ryan Gravenberch (NED) £6.1 2.4%</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Frenkie de Jong (NED) £7.0 1.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.1%</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>[MID] ★Youri Tielemans (BEL) £6.1 1.1%</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>[MID] Kevin De Bruyne (BEL) £7.5 5.6%</t>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[MID] ★Leandro Trossard (BEL) £6.6 2.6%</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>[MID] Brahim Díaz (MAR) £6.4 8.1%</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>[MID] Crysencio Summerville (NED) £5.3 13.6%</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>[MID] Michael Olise (FRA) £9.5 33.0%</t>
         </is>
       </c>
     </row>
@@ -5755,4 +7037,293 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Round-lock snapshot — deterministic re-runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Freezes every stat input at post-R(target-1) state. Re-runs for the same target round are byte-stable except for live %selected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MECHANIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Determine target round</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>pick_target_round() reads LIVE fantasy_rounds.parquet. Picks the round in [start_date, end_date] (active by date), then next scheduled WITH fixtures, then last completed. R32 (R4) only goes live once fantasy_round_matches.parquet has 24 R4 entries — i.e. once the group stage finishes and the bracket fixtures lock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Compute lock_round</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>lock_round = max(0, target - 1). For target=R3 → lock=R2; for target=R4 (R32) → lock=R3; etc. Stats up to AND INCLUDING lock_round are used; everything beyond is filtered out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Validate / create</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Snapshot dir: data/processed/locked/post_round_{lock_round:02d}/. If it exists AND has every parquet lib/recommender.py reads → reuse. If anything's missing (e.g. a new lib dependency landed) → wipe + re-create. Env RELOCK=1 forces a re-create.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Bulk-copy</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Every *.parquet from live PROC → lock_dir. Defensive default so new warehouse parquets don't break the next CI run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Filter per-round source</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>fantasy_player_round_stats.parquet → keep rows with round_id ≤ lock_round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Filter per-match sources</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>wc26_player_match_stats_wide.parquet, wc26_player_match_powerrank.parquet, wc26_stg_team_match_metrics.parquet — keep rows whose match_number is in the round_id ≤ lock_round window (mapped via fantasy_round_matches → squads → stg_matches).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Rebuild aggregates from filtered sources</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>wc26_stg_fantasy_player_totals (appearances / scouting_bonus / total_points / …), wc26_stg_player_powerrank (avg attacking/defensive/creativity/defending_goal_score), wc26_stg_players_view (all 55 fifa_wc_* SUM/AVG/MAX cols + fotmob_wc_appearances override using fifa_wc_n_matches with TimePlayed&gt;0 filter — fixes the bench-row inflation bug).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Rebind PROC</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>lib.recommender.PROC = lock_dir for the scoring + archetype + fixture-profile + squad-assembly calls. Restored to live PROC before history-write so artefacts land in data/processed/ as usual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Manifest</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>_lock_manifest.json stamps target_round, lock_round, created_utc, locked_match_count, and which parquets were filtered vs rebuilt. Inspect this to debug stale locks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>CURRENT LOCK STATE</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>(locked/ directory not present — will be created on first run)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>DETERMINISM AUDIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>R3 suggestions only use up-to-R2 stats?</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>YES. fantasy_player_round_stats filtered to round_id ≤ 2; wide stats filtered to match_number ≤ 48; stg_fantasy_player_totals + stg_player_powerrank + stg_players_view fifa_wc_* rebuilt from those filtered sources. Cumulative tournament aggregates can no longer leak partial R3 data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>R32 (R4) will pick up MD3 stats automatically?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>YES. Once fantasy_round_matches has R4 fixtures (which lands when the group stage finishes), pick_target_round() flips to R4 and a fresh lock dir post_round_03/ is created including all R3 stats. No manual trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Will re-runs of R3 change suggestions?</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>NO for stats — locked. Only live %selected (refresh_live_percent_selected) shifts between runs, which intentionally moves the differential / SB-eligibility math by tiny amounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>What about FotMob-only WC stats not in fifa_wc_*?</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>CLOSED. Two-track rebuild inside the lock: (1) RECOVERABLE counters (goals, assists, minutes_played, yellows, reds, fotmob_rating) re-aggregated from wc26_player_recent_matches_fotmob filtered to WC2026 matches with match_date_utc ≤ lock window end. (2) NON-RECOVERABLE counters (chances_created, big_chances_created, dribbles, duels_won, touches, touches_opp_box, defensive_contributions, tackles, fouls_committed, xg_against_on_pitch) scaled by (lock_apps / live_apps) per player — assumes uniform per-match production, which is the standard unbiased estimator. Rates (duels_won_pct, successful_dribbles_pct) kept as-is — distribution-invariant under uniformity. All 6 fotmob_wc_* cols actually consumed by lib/recommender.py are now genuinely round-bounded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Is the live %selected leak an issue for determinism?</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Intentional. The SB-eligibility gate uses live ownership so picks reflect current market. Stats are frozen; ownership floats.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>